--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D00611A-A1D6-473A-9840-63134879E740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E218DB1E-27CB-4F8B-82E1-C2209BD49756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
   <si>
     <t>Main 활용</t>
   </si>
@@ -60,27 +60,9 @@
 Support</t>
   </si>
   <si>
-    <t>공동주택 지도 시각화 Dasdboard</t>
-  </si>
-  <si>
-    <t>공동주택, 지역난방 시각화, 판매량 비교 등</t>
-  </si>
-  <si>
-    <t>https://daesung-marketing-dashboard.streamlit.app/</t>
-  </si>
-  <si>
     <t>★★★★★</t>
   </si>
   <si>
-    <t>판매량분석(full ver)</t>
-  </si>
-  <si>
-    <t>고객명별, 상품별 전년동월대비 판매량분석</t>
-  </si>
-  <si>
-    <t>https://ghfkd0901.github.io/sale_powerBI/</t>
-  </si>
-  <si>
     <t>판매량분석(simple ver)</t>
   </si>
   <si>
@@ -114,72 +96,9 @@
     <t>★★★</t>
   </si>
   <si>
-    <t>뉴스 모니터링 (Client)</t>
-  </si>
-  <si>
-    <t>대성에너지 주요 고객 뉴스 모니터링(중대재해 등)</t>
-  </si>
-  <si>
-    <t>https://news4daesungclient.streamlit.app/</t>
-  </si>
-  <si>
-    <t>대성에너지 메시지 자동화</t>
-  </si>
-  <si>
-    <t>민원 대응용 문자 발송서비스(053-606-1000)</t>
-  </si>
-  <si>
-    <t>https://daesung-energy-msg-automation.streamlit.app/</t>
-  </si>
-  <si>
-    <t>산업용 열병합 요금 리포트</t>
-  </si>
-  <si>
-    <t>산업용 열병합 발전 가스 요금표 및 변동 추이 리포트</t>
-  </si>
-  <si>
-    <t>https://daesung-industrial-cogeneration-gas-price-report.streamlit.app/</t>
-  </si>
-  <si>
-    <t>도시가스 LPG 경제성 비교</t>
-  </si>
-  <si>
-    <t>식당 영업 시 도시가스 LPG 경제성 비교 및 화력 소개 영상</t>
-  </si>
-  <si>
-    <t>https://daesung-energy-price-checker.streamlit.app/</t>
-  </si>
-  <si>
     <t>★★</t>
   </si>
   <si>
-    <t>전국 보급률 대시보드</t>
-  </si>
-  <si>
-    <t>전국 도시가스 보급률 비교 분석</t>
-  </si>
-  <si>
-    <t>https://korea-city-gas-coverage-dashboard.streamlit.app/</t>
-  </si>
-  <si>
-    <t>전국 효율 대시보드</t>
-  </si>
-  <si>
-    <t>전국 도시가스 공급 효율성 지표 비교 분석</t>
-  </si>
-  <si>
-    <t>https://korea-citygas-efficiency-dashboard.streamlit.app/</t>
-  </si>
-  <si>
-    <t>전국 도시가스 단가표</t>
-  </si>
-  <si>
-    <t>전국 도시가스사별 도시가스 요금 비교</t>
-  </si>
-  <si>
-    <t>https://korea-city-gas-unit-price.streamlit.app/</t>
-  </si>
-  <si>
     <t>HeatBand Insight(난방구간 민감도 분석)</t>
   </si>
   <si>
@@ -193,15 +112,6 @@
   </si>
   <si>
     <t>https://effective-days-choihanyoub.streamlit.app/</t>
-  </si>
-  <si>
-    <t>도시가스공급량_일별계획 예측</t>
-  </si>
-  <si>
-    <t>Daily 공급량 분석, 일별 vs 월별 공급량 분석 비교</t>
-  </si>
-  <si>
-    <t>https://daily-or-monthly-comparative-analysis-choihanyoub.streamlit.app/</t>
   </si>
   <si>
     <t>상세 분류</t>
@@ -221,15 +131,6 @@
     <t>영업 도구(Action &amp; Sales Tool)</t>
   </si>
   <si>
-    <t>산업용 주요고객 분석 대시보드</t>
-  </si>
-  <si>
-    <t>연도별 추이 분석, 연도별 top20, 고객명별 상세 현황 등</t>
-  </si>
-  <si>
-    <t>https://daesung-industry-sale-yearly-top-n.streamlit.app/</t>
-  </si>
-  <si>
     <t>인덕션 전환 추세 분석</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -301,18 +202,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>영업일보</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>계약전, 시설전, 공급전, 폐전, 용도변경 등</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://daesung-sales-report-app.streamlit.app/%EC%98%81%EC%97%85%ED%98%84%ED%99%A9</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>배관투자 승인 내역 관리</t>
   </si>
   <si>
@@ -335,6 +224,556 @@
   </si>
   <si>
     <t>Han _ Smart Marketing Hub</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">신규배관 경제성 분석 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Simulation</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">신규배관 경제성 분석 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Simulation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> ver2</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경제성 분석 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Simple version)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경제성 분석 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Enhanced version) _ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경제성분석 50년 가능</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://simulation-pipeline-investment-dashboard-ver2-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://simulation-pipeline-investment-dashboard-1-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>경제성분석 결재 대시보드</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>배관투자 승인 내역 조회(차수별, 누적)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>공급량 예측(for 사업계획)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공급량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(for MM _ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단기예측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>최저, 최고 기온 입력시 공급량 예측</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>중장기 공급량 예측(2035년)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>중장기 판매량 예측(2035년)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>과거 데이터 업로드시 중장기 공급량 예측</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2035forecast-of-city-gas-sales-volume-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://simulation-pipeline-investment-dashboard-3-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">신규배관 경제성 분석 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Simulation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> ver3</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경제성 분석 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Enhanced version) _ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최소 계량기 추정기능</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://daily-or-monthly-comparative-analysis-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일일 공급량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(for daily </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>일일 공급량 분배_자동조정(for daily 예측 수정)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://daily-or-monthly-comparative-analysis-ver2-check-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://forecast-of-city-gas-supply-and-usage-type-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시가스 공급량 예측(학습기간, 상품 선택)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시가스 계획/실적분석</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>판매량분석, 공급량분석(월), 공급량분석(일)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://mm-supply-forecast-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사업계획(월)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공급량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자동화</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사업계획(월) 일일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공급량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자동화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상치 자동 보정)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gas-supply-forecast-business-plan-choihanyoub.streamlit.app/</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -342,7 +781,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,6 +851,13 @@
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -434,12 +880,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -570,55 +1016,228 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
         <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -627,12 +1246,12 @@
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -644,7 +1263,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -669,62 +1288,89 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -741,14 +1387,83 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1085,7 +1800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1095,13 +1810,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="31"/>
+      <c r="A1" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="40"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1143,445 +1858,429 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="32" t="s">
+    <row r="6" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="56"/>
+      <c r="B7" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="C7" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="D7" s="59" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="33"/>
-      <c r="B7" s="8" t="s">
+      <c r="E7" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="8" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="56"/>
+      <c r="B8" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="C8" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="D8" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="58" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="56"/>
+      <c r="B9" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="56"/>
+      <c r="B10" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="62" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="63"/>
+      <c r="B11" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="50"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+    </row>
+    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="36"/>
+      <c r="B16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="36"/>
+      <c r="B17" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="37"/>
+      <c r="B18" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="47" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="33"/>
-      <c r="B8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="33"/>
-      <c r="B9" s="8" t="s">
+      <c r="E19" s="48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="36"/>
+      <c r="B20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="36"/>
+      <c r="B21" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="36"/>
+      <c r="B22" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="36"/>
+      <c r="B23" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="36"/>
+      <c r="B24" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="36"/>
+      <c r="B25" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="8" t="s">
+    </row>
+    <row r="27" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="36"/>
+      <c r="B27" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="36"/>
+      <c r="B28" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="33"/>
-      <c r="B10" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="33"/>
-      <c r="B11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="34"/>
-      <c r="B12" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="27"/>
-      <c r="B17" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="27"/>
-      <c r="B18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="28"/>
-      <c r="B19" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="27"/>
-      <c r="B21" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="27"/>
-      <c r="B22" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="27"/>
-      <c r="B23" s="18" t="s">
+    </row>
+    <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="36"/>
+      <c r="B29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="36"/>
+      <c r="B30" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="36"/>
+      <c r="B31" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="37"/>
+      <c r="B32" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="27"/>
-      <c r="B24" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="28"/>
-      <c r="B25" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="26" t="s">
+      <c r="D32" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="27"/>
-      <c r="B27" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="27"/>
-      <c r="B28" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="27"/>
-      <c r="B29" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="27"/>
-      <c r="B30" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="28"/>
-      <c r="B31" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="13" t="s">
+      <c r="E32" s="35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="D32" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="27"/>
-      <c r="B33" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="28"/>
-      <c r="B34" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="29"/>
+    </row>
+    <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="36"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="14"/>
+    </row>
+    <row r="35" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="37"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="24"/>
     </row>
     <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
@@ -1597,42 +2296,47 @@
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
+    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A33:A35"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:A12"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A26:A31"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="A26:A32"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D6" r:id="rId1" xr:uid="{F1E97151-816F-47B2-B425-70BA6507D2DC}"/>
-    <hyperlink ref="D7" r:id="rId2" xr:uid="{5C1DEC94-2F4B-4133-86D3-AADE1EC5BB7B}"/>
-    <hyperlink ref="D8" r:id="rId3" xr:uid="{A029C8B6-F468-4C9C-BCDF-9334B981A7AA}"/>
-    <hyperlink ref="D9" r:id="rId4" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
-    <hyperlink ref="D11" r:id="rId5" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D12" r:id="rId6" xr:uid="{18DA179E-DE32-4D35-B9E1-21A5601866FD}"/>
-    <hyperlink ref="D16" r:id="rId7" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
-    <hyperlink ref="D18" r:id="rId8" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
-    <hyperlink ref="D19" r:id="rId9" xr:uid="{7556C996-B8A7-434D-9D62-16C7A446460A}"/>
-    <hyperlink ref="D20" r:id="rId10" xr:uid="{C1FBCA7A-6843-4B17-AF91-EE372BADDDE6}"/>
-    <hyperlink ref="D21" r:id="rId11" xr:uid="{34ED876C-4C80-40B4-9214-C90A9ACD0562}"/>
-    <hyperlink ref="D22" r:id="rId12" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D25" r:id="rId13" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
-    <hyperlink ref="D26" r:id="rId14" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D28" r:id="rId15" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D29" r:id="rId16" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
-    <hyperlink ref="D30" r:id="rId17" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
-    <hyperlink ref="D31" r:id="rId18" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
-    <hyperlink ref="D32" r:id="rId19" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
-    <hyperlink ref="D33" r:id="rId20" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
-    <hyperlink ref="D34" r:id="rId21" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
-    <hyperlink ref="D23" r:id="rId22" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
-    <hyperlink ref="D27" r:id="rId23" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
-    <hyperlink ref="D24" r:id="rId24" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
-    <hyperlink ref="D17" r:id="rId25" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D7" r:id="rId1" xr:uid="{A029C8B6-F468-4C9C-BCDF-9334B981A7AA}"/>
+    <hyperlink ref="D8" r:id="rId2" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
+    <hyperlink ref="D11" r:id="rId3" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D15" r:id="rId4" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
+    <hyperlink ref="D17" r:id="rId5" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
+    <hyperlink ref="D19" r:id="rId6" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
+    <hyperlink ref="D26" r:id="rId7" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D28" r:id="rId8" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D27" r:id="rId9" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D16" r:id="rId10" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D31" r:id="rId11" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
+    <hyperlink ref="D30" r:id="rId12" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
+    <hyperlink ref="D29" r:id="rId13" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
+    <hyperlink ref="D24" r:id="rId14" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
+    <hyperlink ref="D25" r:id="rId15" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
+    <hyperlink ref="D32" r:id="rId16" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
+    <hyperlink ref="D21" r:id="rId17" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
+    <hyperlink ref="D22" r:id="rId18" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
+    <hyperlink ref="D20" r:id="rId19" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
+    <hyperlink ref="D23" r:id="rId20" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
+    <hyperlink ref="D18" r:id="rId21" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
+    <hyperlink ref="D6" r:id="rId22" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
+    <hyperlink ref="D10" r:id="rId23" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E218DB1E-27CB-4F8B-82E1-C2209BD49756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889EAD19-127F-4C81-8229-9C06207CD30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="74">
   <si>
     <t>Main 활용</t>
   </si>
@@ -774,6 +774,10 @@
   </si>
   <si>
     <t>https://gas-supply-forecast-business-plan-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/view?r=eyJrIjoiOWIwMDZkYTEtZjM1ZS00NGE3LTg4ODktYTQ2ZjI2OWY5ZDdmIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1372,6 +1376,72 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1387,83 +1457,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1810,13 +1814,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="40"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1859,103 +1863,103 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="48" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="56"/>
-      <c r="B7" s="57" t="s">
+      <c r="A7" s="64"/>
+      <c r="B7" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="59" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="58" t="s">
+      <c r="D7" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="50" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57" t="s">
+      <c r="A8" s="64"/>
+      <c r="B8" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="58" t="s">
+      <c r="E8" s="50" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57" t="s">
+      <c r="A9" s="64"/>
+      <c r="B9" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="50" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="56"/>
-      <c r="B10" s="60" t="s">
+      <c r="A10" s="64"/>
+      <c r="B10" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="E10" s="54" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64" t="s">
+      <c r="A11" s="65"/>
+      <c r="B11" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="66" t="s">
+      <c r="D11" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="E11" s="56" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="50"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
     </row>
     <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
@@ -1984,7 +1988,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="66" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -2001,7 +2005,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
+      <c r="A16" s="58"/>
       <c r="B16" s="11" t="s">
         <v>37</v>
       </c>
@@ -2016,7 +2020,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
+      <c r="A17" s="58"/>
       <c r="B17" s="15" t="s">
         <v>15</v>
       </c>
@@ -2031,22 +2035,22 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="37"/>
-      <c r="B18" s="44" t="s">
+      <c r="A18" s="59"/>
+      <c r="B18" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C18" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D18" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="49" t="s">
+      <c r="E18" s="43" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="58" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="28" t="s">
@@ -2055,15 +2059,15 @@
       <c r="C19" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="48" t="s">
+      <c r="E19" s="42" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
+      <c r="A20" s="58"/>
       <c r="B20" s="11" t="s">
         <v>51</v>
       </c>
@@ -2078,14 +2082,14 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
+      <c r="A21" s="58"/>
       <c r="B21" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="42" t="s">
+      <c r="D21" s="36" t="s">
         <v>61</v>
       </c>
       <c r="E21" s="32" t="s">
@@ -2093,14 +2097,14 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="36"/>
+      <c r="A22" s="58"/>
       <c r="B22" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="42" t="s">
+      <c r="D22" s="36" t="s">
         <v>64</v>
       </c>
       <c r="E22" s="32" t="s">
@@ -2108,7 +2112,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
+      <c r="A23" s="58"/>
       <c r="B23" s="17" t="s">
         <v>52</v>
       </c>
@@ -2123,7 +2127,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
+      <c r="A24" s="58"/>
       <c r="B24" s="11" t="s">
         <v>54</v>
       </c>
@@ -2138,7 +2142,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="36"/>
+      <c r="A25" s="58"/>
       <c r="B25" s="11" t="s">
         <v>55</v>
       </c>
@@ -2153,7 +2157,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="66" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -2170,7 +2174,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
+      <c r="A27" s="58"/>
       <c r="B27" s="11" t="s">
         <v>30</v>
       </c>
@@ -2185,7 +2189,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="36"/>
+      <c r="A28" s="58"/>
       <c r="B28" s="15" t="s">
         <v>23</v>
       </c>
@@ -2200,7 +2204,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
+      <c r="A29" s="58"/>
       <c r="B29" s="11" t="s">
         <v>49</v>
       </c>
@@ -2215,7 +2219,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
+      <c r="A30" s="58"/>
       <c r="B30" s="17" t="s">
         <v>43</v>
       </c>
@@ -2230,7 +2234,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
+      <c r="A31" s="58"/>
       <c r="B31" s="17" t="s">
         <v>44</v>
       </c>
@@ -2245,7 +2249,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="37"/>
+      <c r="A32" s="59"/>
       <c r="B32" s="33" t="s">
         <v>59</v>
       </c>
@@ -2260,7 +2264,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="36" t="s">
+      <c r="A33" s="58" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="28"/>
@@ -2269,14 +2273,14 @@
       <c r="E33" s="29"/>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="36"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="15"/>
       <c r="C34" s="14"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="37"/>
+      <c r="A35" s="59"/>
       <c r="B35" s="23"/>
       <c r="C35" s="24"/>
       <c r="D35" s="25"/>
@@ -2314,29 +2318,29 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D7" r:id="rId1" xr:uid="{A029C8B6-F468-4C9C-BCDF-9334B981A7AA}"/>
-    <hyperlink ref="D8" r:id="rId2" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
-    <hyperlink ref="D11" r:id="rId3" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D15" r:id="rId4" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
-    <hyperlink ref="D17" r:id="rId5" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
-    <hyperlink ref="D19" r:id="rId6" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D26" r:id="rId7" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D28" r:id="rId8" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D27" r:id="rId9" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
-    <hyperlink ref="D16" r:id="rId10" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
-    <hyperlink ref="D31" r:id="rId11" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
-    <hyperlink ref="D30" r:id="rId12" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
-    <hyperlink ref="D29" r:id="rId13" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
-    <hyperlink ref="D24" r:id="rId14" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
-    <hyperlink ref="D25" r:id="rId15" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
-    <hyperlink ref="D32" r:id="rId16" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
-    <hyperlink ref="D21" r:id="rId17" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
-    <hyperlink ref="D22" r:id="rId18" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
-    <hyperlink ref="D20" r:id="rId19" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
-    <hyperlink ref="D23" r:id="rId20" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
-    <hyperlink ref="D18" r:id="rId21" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
-    <hyperlink ref="D6" r:id="rId22" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
-    <hyperlink ref="D10" r:id="rId23" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
+    <hyperlink ref="D8" r:id="rId1" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
+    <hyperlink ref="D11" r:id="rId2" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D15" r:id="rId3" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
+    <hyperlink ref="D17" r:id="rId4" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
+    <hyperlink ref="D19" r:id="rId5" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
+    <hyperlink ref="D26" r:id="rId6" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D28" r:id="rId7" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D27" r:id="rId8" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D16" r:id="rId9" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D31" r:id="rId10" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
+    <hyperlink ref="D30" r:id="rId11" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
+    <hyperlink ref="D29" r:id="rId12" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
+    <hyperlink ref="D24" r:id="rId13" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
+    <hyperlink ref="D25" r:id="rId14" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
+    <hyperlink ref="D32" r:id="rId15" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
+    <hyperlink ref="D21" r:id="rId16" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
+    <hyperlink ref="D22" r:id="rId17" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
+    <hyperlink ref="D20" r:id="rId18" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
+    <hyperlink ref="D23" r:id="rId19" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
+    <hyperlink ref="D18" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
+    <hyperlink ref="D6" r:id="rId21" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
+    <hyperlink ref="D10" r:id="rId22" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
+    <hyperlink ref="D7" r:id="rId23" xr:uid="{562E5992-9F61-4F36-84A6-7148F6E45583}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889EAD19-127F-4C81-8229-9C06207CD30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA45020F-4BD0-4AC3-877D-BCE1246232CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -2340,7 +2340,7 @@
     <hyperlink ref="D18" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
     <hyperlink ref="D6" r:id="rId21" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
     <hyperlink ref="D10" r:id="rId22" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
-    <hyperlink ref="D7" r:id="rId23" xr:uid="{562E5992-9F61-4F36-84A6-7148F6E45583}"/>
+    <hyperlink ref="D7" r:id="rId23" xr:uid="{5776487D-7E23-4422-984E-D52DCEC1F73F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA45020F-4BD0-4AC3-877D-BCE1246232CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30101F24-94C2-41C0-8F7C-87797633B47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -777,7 +777,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>https://app.powerbi.com/view?r=eyJrIjoiOWIwMDZkYTEtZjM1ZS00NGE3LTg4ODktYTQ2ZjI2OWY5ZDdmIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
+    <t>https://app.powerbi.com/groups/me/reports/ffbf9cef-c59a-41a6-8cd3-765a31633a25/ReportSectioncc56c28d5f143af928f4?experience=power-bi</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2340,7 +2340,7 @@
     <hyperlink ref="D18" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
     <hyperlink ref="D6" r:id="rId21" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
     <hyperlink ref="D10" r:id="rId22" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
-    <hyperlink ref="D7" r:id="rId23" xr:uid="{5776487D-7E23-4422-984E-D52DCEC1F73F}"/>
+    <hyperlink ref="D7" r:id="rId23" xr:uid="{8187D672-2E7D-4FE4-AEC8-DAE4DC377866}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30101F24-94C2-41C0-8F7C-87797633B47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC51AD20-1DD0-482E-A53E-5AE1D0B78E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -777,7 +777,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>https://app.powerbi.com/groups/me/reports/ffbf9cef-c59a-41a6-8cd3-765a31633a25/ReportSectioncc56c28d5f143af928f4?experience=power-bi</t>
+    <t>https://app.powerbi.com/reportEmbed?reportId=ffbf9cef-c59a-41a6-8cd3-765a31633a25&amp;autoAuth=true&amp;ctid=966ea1f4-b921-40f1-8321-cb1ef2a79660</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC51AD20-1DD0-482E-A53E-5AE1D0B78E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41B8EE2-B879-4071-951D-51799948D037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t>Main 활용</t>
   </si>
@@ -778,6 +778,39 @@
   </si>
   <si>
     <t>https://app.powerbi.com/reportEmbed?reportId=ffbf9cef-c59a-41a6-8cd3-765a31633a25&amp;autoAuth=true&amp;ctid=966ea1f4-b921-40f1-8321-cb1ef2a79660</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시가스 판매량 분석 보고서</t>
+  </si>
+  <si>
+    <t>도시가스 판매량 분석 보고서</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>판매량분석, 용도별분석, 산업용/업무용 업종분석 등</t>
+  </si>
+  <si>
+    <t>판매량분석, 용도별분석, 산업용/업무용 업종분석 등</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://quarterly-sales-report-choihanyoub.streamlit.app/</t>
+  </si>
+  <si>
+    <t>https://quarterly-sales-report-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>기온 분석 및 이상기온 모니터링 대시보드</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상기온 분석, 일별 기온 분석(기온매트릭스)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://temperature-analysis-choihanyoub.streamlit.app/</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1267,7 +1300,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1468,6 +1501,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1804,7 +1849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1881,14 +1926,14 @@
     </row>
     <row r="7" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="64"/>
-      <c r="B7" s="49" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="51" t="s">
-        <v>73</v>
+      <c r="B7" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>79</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>11</v>
@@ -1897,215 +1942,215 @@
     <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64"/>
       <c r="B8" s="49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="E8" s="50" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="64"/>
       <c r="B9" s="49" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="64"/>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="64"/>
+      <c r="B11" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C11" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D11" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="54" t="s">
+      <c r="E11" s="54" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="65"/>
-      <c r="B11" s="55" t="s">
+    <row r="12" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="65"/>
+      <c r="B12" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C12" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="57" t="s">
+      <c r="D12" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="56" t="s">
+      <c r="E12" s="56" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="44"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-    </row>
     <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+    </row>
+    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B15" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C15" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D15" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E15" s="27" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="66" t="s">
+    <row r="16" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="58"/>
-      <c r="B16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58"/>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="58"/>
+      <c r="B18" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="58"/>
+      <c r="B19" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C19" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D19" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E19" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="59"/>
-      <c r="B18" s="38" t="s">
+    <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="59"/>
+      <c r="B20" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C20" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D20" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E20" s="43" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58" t="s">
+    <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B21" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C21" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="D21" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="42" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="58"/>
-      <c r="B20" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58"/>
-      <c r="B21" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="42" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="58"/>
-      <c r="B22" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>64</v>
+      <c r="B22" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="70" t="s">
+        <v>78</v>
       </c>
       <c r="E22" s="32" t="s">
         <v>11</v>
@@ -2113,234 +2158,281 @@
     </row>
     <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58"/>
-      <c r="B23" s="17" t="s">
-        <v>52</v>
+      <c r="B23" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>34</v>
+        <v>65</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="58"/>
-      <c r="B24" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58"/>
       <c r="B25" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="58"/>
+      <c r="B26" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="19" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="58"/>
       <c r="B27" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>33</v>
+        <v>54</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="58"/>
-      <c r="B28" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>19</v>
+      <c r="B28" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="58"/>
-      <c r="B29" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>35</v>
+      <c r="A29" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="58"/>
-      <c r="B30" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>45</v>
+      <c r="B30" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="58"/>
-      <c r="B31" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>46</v>
+      <c r="B31" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="58"/>
+      <c r="B32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="59"/>
-      <c r="B32" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32" s="35" t="s">
-        <v>35</v>
-      </c>
-    </row>
     <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="29"/>
+      <c r="A33" s="58"/>
+      <c r="B33" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="58"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="14"/>
+      <c r="B34" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="59"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="24"/>
-    </row>
-    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="B35" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" s="35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="29"/>
+    </row>
+    <row r="37" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="58"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="14"/>
+    </row>
+    <row r="38" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="59"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
+    </row>
+    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A36:A38"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="A26:A32"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A21:A28"/>
+    <mergeCell ref="A29:A35"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D8" r:id="rId1" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
-    <hyperlink ref="D11" r:id="rId2" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D15" r:id="rId3" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
-    <hyperlink ref="D17" r:id="rId4" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
-    <hyperlink ref="D19" r:id="rId5" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D26" r:id="rId6" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D28" r:id="rId7" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D27" r:id="rId8" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
-    <hyperlink ref="D16" r:id="rId9" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
-    <hyperlink ref="D31" r:id="rId10" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
-    <hyperlink ref="D30" r:id="rId11" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
-    <hyperlink ref="D29" r:id="rId12" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
-    <hyperlink ref="D24" r:id="rId13" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
-    <hyperlink ref="D25" r:id="rId14" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
-    <hyperlink ref="D32" r:id="rId15" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
-    <hyperlink ref="D21" r:id="rId16" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
-    <hyperlink ref="D22" r:id="rId17" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
-    <hyperlink ref="D20" r:id="rId18" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
-    <hyperlink ref="D23" r:id="rId19" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
-    <hyperlink ref="D18" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
+    <hyperlink ref="D12" r:id="rId2" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D16" r:id="rId3" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
+    <hyperlink ref="D19" r:id="rId4" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
+    <hyperlink ref="D21" r:id="rId5" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
+    <hyperlink ref="D29" r:id="rId6" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D31" r:id="rId7" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D30" r:id="rId8" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D17" r:id="rId9" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D34" r:id="rId10" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
+    <hyperlink ref="D33" r:id="rId11" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
+    <hyperlink ref="D32" r:id="rId12" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
+    <hyperlink ref="D27" r:id="rId13" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
+    <hyperlink ref="D28" r:id="rId14" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
+    <hyperlink ref="D35" r:id="rId15" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
+    <hyperlink ref="D24" r:id="rId16" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
+    <hyperlink ref="D25" r:id="rId17" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
+    <hyperlink ref="D23" r:id="rId18" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
+    <hyperlink ref="D26" r:id="rId19" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
+    <hyperlink ref="D20" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
     <hyperlink ref="D6" r:id="rId21" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
-    <hyperlink ref="D10" r:id="rId22" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
-    <hyperlink ref="D7" r:id="rId23" xr:uid="{8187D672-2E7D-4FE4-AEC8-DAE4DC377866}"/>
+    <hyperlink ref="D11" r:id="rId22" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
+    <hyperlink ref="D8" r:id="rId23" xr:uid="{8187D672-2E7D-4FE4-AEC8-DAE4DC377866}"/>
+    <hyperlink ref="D7" r:id="rId24" xr:uid="{393AFF9D-C13B-4F2D-B7F2-228345157345}"/>
+    <hyperlink ref="D18" r:id="rId25" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41B8EE2-B879-4071-951D-51799948D037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CBCCE8-A147-497B-A911-5184B6E98912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -777,10 +777,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>https://app.powerbi.com/reportEmbed?reportId=ffbf9cef-c59a-41a6-8cd3-765a31633a25&amp;autoAuth=true&amp;ctid=966ea1f4-b921-40f1-8321-cb1ef2a79660</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>도시가스 판매량 분석 보고서</t>
   </si>
   <si>
@@ -812,6 +808,9 @@
   <si>
     <t>https://temperature-analysis-choihanyoub.streamlit.app/</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/view?r=eyJrIjoiOWIwMDZkYTEtZjM1ZS00NGE3LTg4ODktYTQ2ZjI2OWY5ZDdmIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
   </si>
 </sst>
 </file>
@@ -1475,6 +1474,18 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1501,18 +1512,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1859,13 +1858,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="62"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1908,7 +1907,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="45" t="s">
@@ -1925,22 +1924,22 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="64"/>
-      <c r="B7" s="67" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="68" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="69" t="s">
-        <v>79</v>
+      <c r="A7" s="68"/>
+      <c r="B7" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="60" t="s">
+        <v>78</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="64"/>
+      <c r="A8" s="68"/>
       <c r="B8" s="49" t="s">
         <v>8</v>
       </c>
@@ -1948,14 +1947,14 @@
         <v>9</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="64"/>
+      <c r="A9" s="68"/>
       <c r="B9" s="49" t="s">
         <v>12</v>
       </c>
@@ -1970,7 +1969,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="64"/>
+      <c r="A10" s="68"/>
       <c r="B10" s="49" t="s">
         <v>36</v>
       </c>
@@ -1985,7 +1984,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="64"/>
+      <c r="A11" s="68"/>
       <c r="B11" s="52" t="s">
         <v>59</v>
       </c>
@@ -2000,7 +1999,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="65"/>
+      <c r="A12" s="69"/>
       <c r="B12" s="55" t="s">
         <v>15</v>
       </c>
@@ -2048,7 +2047,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="70" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -2065,7 +2064,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="58"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="11" t="s">
         <v>37</v>
       </c>
@@ -2080,22 +2079,22 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="58"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>81</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>82</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58"/>
+      <c r="A19" s="62"/>
       <c r="B19" s="15" t="s">
         <v>15</v>
       </c>
@@ -2110,7 +2109,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="59"/>
+      <c r="A20" s="63"/>
       <c r="B20" s="38" t="s">
         <v>67</v>
       </c>
@@ -2125,7 +2124,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58" t="s">
+      <c r="A21" s="62" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="28" t="s">
@@ -2142,22 +2141,22 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="58"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="70" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+      <c r="D22" s="61" t="s">
+        <v>77</v>
       </c>
       <c r="E22" s="32" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="58"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="11" t="s">
         <v>51</v>
       </c>
@@ -2172,7 +2171,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="58"/>
+      <c r="A24" s="62"/>
       <c r="B24" s="17" t="s">
         <v>62</v>
       </c>
@@ -2187,7 +2186,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="58"/>
+      <c r="A25" s="62"/>
       <c r="B25" s="11" t="s">
         <v>63</v>
       </c>
@@ -2202,7 +2201,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="58"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="17" t="s">
         <v>52</v>
       </c>
@@ -2217,7 +2216,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="58"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="11" t="s">
         <v>54</v>
       </c>
@@ -2232,7 +2231,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="58"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="11" t="s">
         <v>55</v>
       </c>
@@ -2247,7 +2246,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="66" t="s">
+      <c r="A29" s="70" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -2264,7 +2263,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="58"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="11" t="s">
         <v>30</v>
       </c>
@@ -2279,7 +2278,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="58"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="15" t="s">
         <v>23</v>
       </c>
@@ -2294,7 +2293,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="58"/>
+      <c r="A32" s="62"/>
       <c r="B32" s="11" t="s">
         <v>49</v>
       </c>
@@ -2309,7 +2308,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="58"/>
+      <c r="A33" s="62"/>
       <c r="B33" s="17" t="s">
         <v>43</v>
       </c>
@@ -2324,7 +2323,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="58"/>
+      <c r="A34" s="62"/>
       <c r="B34" s="17" t="s">
         <v>44</v>
       </c>
@@ -2339,7 +2338,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="59"/>
+      <c r="A35" s="63"/>
       <c r="B35" s="33" t="s">
         <v>59</v>
       </c>
@@ -2354,7 +2353,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="58" t="s">
+      <c r="A36" s="62" t="s">
         <v>29</v>
       </c>
       <c r="B36" s="28"/>
@@ -2363,14 +2362,14 @@
       <c r="E36" s="29"/>
     </row>
     <row r="37" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="58"/>
+      <c r="A37" s="62"/>
       <c r="B37" s="15"/>
       <c r="C37" s="14"/>
       <c r="D37" s="13"/>
       <c r="E37" s="14"/>
     </row>
     <row r="38" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="59"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="23"/>
       <c r="C38" s="24"/>
       <c r="D38" s="25"/>
@@ -2430,9 +2429,8 @@
     <hyperlink ref="D20" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
     <hyperlink ref="D6" r:id="rId21" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
     <hyperlink ref="D11" r:id="rId22" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
-    <hyperlink ref="D8" r:id="rId23" xr:uid="{8187D672-2E7D-4FE4-AEC8-DAE4DC377866}"/>
-    <hyperlink ref="D7" r:id="rId24" xr:uid="{393AFF9D-C13B-4F2D-B7F2-228345157345}"/>
-    <hyperlink ref="D18" r:id="rId25" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
+    <hyperlink ref="D7" r:id="rId23" xr:uid="{393AFF9D-C13B-4F2D-B7F2-228345157345}"/>
+    <hyperlink ref="D18" r:id="rId24" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CBCCE8-A147-497B-A911-5184B6E98912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37638205-5116-4708-AF41-5D9DF79D26B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="85">
   <si>
     <t>Main 활용</t>
   </si>
@@ -811,6 +811,14 @@
   </si>
   <si>
     <t>https://app.powerbi.com/view?r=eyJrIjoiOWIwMDZkYTEtZjM1ZS00NGE3LTg4ODktYTQ2ZjI2OWY5ZDdmIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기온분석 및 이상기온 모니터링 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>기온매트릭스, 평균기온, 이상기온 분석</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -921,7 +929,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1290,6 +1298,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1299,7 +1320,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1512,6 +1533,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1848,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1998,96 +2028,96 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="69"/>
-      <c r="B12" s="55" t="s">
+    <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="68"/>
+      <c r="B12" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="71" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="69"/>
+      <c r="B13" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C13" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D13" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E13" s="56" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-    </row>
     <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="44"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+    </row>
+    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="26" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B16" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C16" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D16" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E16" s="27" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="70" t="s">
+    <row r="17" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="62"/>
-      <c r="B17" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="62"/>
       <c r="B18" s="11" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>18</v>
@@ -2095,76 +2125,76 @@
     </row>
     <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="62"/>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="62"/>
+      <c r="B20" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C20" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D20" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="63"/>
-      <c r="B20" s="38" t="s">
+    <row r="21" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="63"/>
+      <c r="B21" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C21" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="D21" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E21" s="43" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="62" t="s">
+    <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B22" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C22" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="D22" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="42" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="62"/>
-      <c r="B22" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="42" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="62"/>
-      <c r="B23" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>65</v>
+      <c r="B23" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="61" t="s">
+        <v>77</v>
       </c>
       <c r="E23" s="32" t="s">
         <v>11</v>
@@ -2172,14 +2202,14 @@
     </row>
     <row r="24" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="62"/>
-      <c r="B24" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="36" t="s">
-        <v>61</v>
+      <c r="B24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="E24" s="32" t="s">
         <v>11</v>
@@ -2187,14 +2217,14 @@
     </row>
     <row r="25" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="62"/>
-      <c r="B25" s="11" t="s">
-        <v>63</v>
+      <c r="B25" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E25" s="32" t="s">
         <v>11</v>
@@ -2202,38 +2232,38 @@
     </row>
     <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="62"/>
-      <c r="B26" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>34</v>
+      <c r="B26" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="62"/>
-      <c r="B27" s="11" t="s">
-        <v>54</v>
+      <c r="B27" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="62"/>
       <c r="B28" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>56</v>
@@ -2245,142 +2275,150 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="70" t="s">
+    <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="62"/>
+      <c r="B29" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B30" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C30" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D30" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E30" s="9" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="62"/>
-      <c r="B30" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="62"/>
-      <c r="B31" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>32</v>
+      <c r="B31" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="62"/>
-      <c r="B32" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>50</v>
+      <c r="B32" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>35</v>
+        <v>24</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="62"/>
-      <c r="B33" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>45</v>
+      <c r="B33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>50</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="62"/>
       <c r="B34" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="62"/>
+      <c r="B35" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C35" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D35" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E35" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="63"/>
-      <c r="B35" s="33" t="s">
+    <row r="36" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="63"/>
+      <c r="B36" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C36" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D36" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="E35" s="35" t="s">
+      <c r="E36" s="35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="62" t="s">
+    <row r="37" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="29"/>
-    </row>
-    <row r="37" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="62"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="14"/>
-    </row>
-    <row r="38" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="63"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="24"/>
-    </row>
-    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="29"/>
+    </row>
+    <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="62"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="14"/>
+    </row>
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="63"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
@@ -2396,41 +2434,49 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A37:A39"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:A12"/>
-    <mergeCell ref="A16:A20"/>
-    <mergeCell ref="A21:A28"/>
-    <mergeCell ref="A29:A35"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A29"/>
+    <mergeCell ref="A30:A36"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D9" r:id="rId1" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
-    <hyperlink ref="D12" r:id="rId2" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D16" r:id="rId3" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
-    <hyperlink ref="D19" r:id="rId4" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
-    <hyperlink ref="D21" r:id="rId5" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D29" r:id="rId6" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D31" r:id="rId7" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D30" r:id="rId8" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
-    <hyperlink ref="D17" r:id="rId9" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
-    <hyperlink ref="D34" r:id="rId10" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
-    <hyperlink ref="D33" r:id="rId11" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
-    <hyperlink ref="D32" r:id="rId12" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
-    <hyperlink ref="D27" r:id="rId13" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
-    <hyperlink ref="D28" r:id="rId14" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
-    <hyperlink ref="D35" r:id="rId15" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
-    <hyperlink ref="D24" r:id="rId16" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
-    <hyperlink ref="D25" r:id="rId17" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
-    <hyperlink ref="D23" r:id="rId18" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
-    <hyperlink ref="D26" r:id="rId19" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
-    <hyperlink ref="D20" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
+    <hyperlink ref="D13" r:id="rId2" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D17" r:id="rId3" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
+    <hyperlink ref="D20" r:id="rId4" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
+    <hyperlink ref="D22" r:id="rId5" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
+    <hyperlink ref="D30" r:id="rId6" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D32" r:id="rId7" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D31" r:id="rId8" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D18" r:id="rId9" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D35" r:id="rId10" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
+    <hyperlink ref="D34" r:id="rId11" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
+    <hyperlink ref="D33" r:id="rId12" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
+    <hyperlink ref="D28" r:id="rId13" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
+    <hyperlink ref="D29" r:id="rId14" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
+    <hyperlink ref="D36" r:id="rId15" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
+    <hyperlink ref="D25" r:id="rId16" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
+    <hyperlink ref="D26" r:id="rId17" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
+    <hyperlink ref="D24" r:id="rId18" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
+    <hyperlink ref="D27" r:id="rId19" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
+    <hyperlink ref="D21" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
     <hyperlink ref="D6" r:id="rId21" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
     <hyperlink ref="D11" r:id="rId22" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
     <hyperlink ref="D7" r:id="rId23" xr:uid="{393AFF9D-C13B-4F2D-B7F2-228345157345}"/>
-    <hyperlink ref="D18" r:id="rId24" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
+    <hyperlink ref="D19" r:id="rId24" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
+    <hyperlink ref="D12" r:id="rId25" xr:uid="{4530051B-988E-4F1C-B60C-9AAE0AF4CF53}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37638205-5116-4708-AF41-5D9DF79D26B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77935F9-4A00-4CC7-98C7-C128A22BEFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
+    <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="88">
   <si>
     <t>Main 활용</t>
   </si>
@@ -818,6 +818,18 @@
   </si>
   <si>
     <t>기온매트릭스, 평균기온, 이상기온 분석</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>대표이사 보고용 _ 판매량 분석</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>최근3~5Y 판매량 분석 및 용도별 구성비 분석 등</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dse-sales-report-choihanyoub.streamlit.app/</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1507,6 +1519,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1533,15 +1554,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1878,7 +1890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1888,13 +1900,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="66"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1937,7 +1949,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="70" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="45" t="s">
@@ -1954,7 +1966,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="68"/>
+      <c r="A7" s="71"/>
       <c r="B7" s="58" t="s">
         <v>74</v>
       </c>
@@ -1969,316 +1981,316 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="68"/>
-      <c r="B8" s="49" t="s">
+      <c r="A8" s="71"/>
+      <c r="B8" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="71"/>
+      <c r="B9" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C9" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D9" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E9" s="50" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="68"/>
-      <c r="B9" s="49" t="s">
+    <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="71"/>
+      <c r="B10" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C10" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D10" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E10" s="50" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="68"/>
-      <c r="B10" s="49" t="s">
+    <row r="11" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="71"/>
+      <c r="B11" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C11" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D11" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E11" s="50" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="68"/>
-      <c r="B11" s="52" t="s">
+    <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="71"/>
+      <c r="B12" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C12" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D12" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="54" t="s">
+      <c r="E12" s="54" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="68"/>
-      <c r="B12" s="72" t="s">
+    <row r="13" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="71"/>
+      <c r="B13" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C13" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="71" t="s">
+      <c r="D13" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E13" s="50" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="69"/>
-      <c r="B13" s="55" t="s">
+    <row r="14" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="72"/>
+      <c r="B14" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C14" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="D14" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="56" t="s">
+      <c r="E14" s="56" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="44"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-    </row>
     <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+    </row>
+    <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B17" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C17" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D17" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E17" s="27" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="70" t="s">
+    <row r="18" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D18" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E18" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="62"/>
-      <c r="B18" s="11" t="s">
+    <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="65"/>
+      <c r="B19" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C19" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D19" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="62"/>
-      <c r="B19" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="62"/>
-      <c r="B20" s="15" t="s">
+      <c r="A20" s="65"/>
+      <c r="B20" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="65"/>
+      <c r="B21" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C21" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D21" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E21" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="63"/>
-      <c r="B21" s="38" t="s">
+    <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="66"/>
+      <c r="B22" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C22" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D22" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="43" t="s">
+      <c r="E22" s="43" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="62" t="s">
+    <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B23" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C23" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="41" t="s">
+      <c r="D23" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="42" t="s">
+      <c r="E23" s="42" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="62"/>
-      <c r="B23" s="28" t="s">
+    <row r="24" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="65"/>
+      <c r="B24" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C24" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="61" t="s">
+      <c r="D24" s="61" t="s">
         <v>77</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="62"/>
-      <c r="B24" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>65</v>
       </c>
       <c r="E24" s="32" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="62"/>
-      <c r="B25" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>61</v>
+      <c r="A25" s="65"/>
+      <c r="B25" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="E25" s="32" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="62"/>
-      <c r="B26" s="11" t="s">
-        <v>63</v>
+      <c r="A26" s="65"/>
+      <c r="B26" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E26" s="32" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="62"/>
-      <c r="B27" s="17" t="s">
+      <c r="A27" s="65"/>
+      <c r="B27" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="65"/>
+      <c r="B28" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C28" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D28" s="16" t="s">
         <v>69</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="62"/>
-      <c r="B28" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="62"/>
+    <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="65"/>
       <c r="B29" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>56</v>
@@ -2290,142 +2302,150 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="70" t="s">
+    <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="65"/>
+      <c r="B30" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B31" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C31" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D31" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E31" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="62"/>
-      <c r="B31" s="11" t="s">
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="65"/>
+      <c r="B32" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C32" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D32" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E32" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="62"/>
-      <c r="B32" s="15" t="s">
+    <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="65"/>
+      <c r="B33" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D33" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E33" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="62"/>
-      <c r="B33" s="11" t="s">
+    <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="65"/>
+      <c r="B34" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C34" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D34" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E34" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="62"/>
-      <c r="B34" s="17" t="s">
+    <row r="35" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="65"/>
+      <c r="B35" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C35" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D35" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E35" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="62"/>
-      <c r="B35" s="17" t="s">
+    <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="65"/>
+      <c r="B36" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C36" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D36" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E36" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="63"/>
-      <c r="B36" s="33" t="s">
+    <row r="37" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="66"/>
+      <c r="B37" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C37" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="25" t="s">
+      <c r="D37" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="E36" s="35" t="s">
+      <c r="E37" s="35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="62" t="s">
+    <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="29"/>
-    </row>
-    <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="62"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="14"/>
-    </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="63"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="24"/>
-    </row>
-    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="29"/>
+    </row>
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="65"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="14"/>
+    </row>
+    <row r="40" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="66"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="24"/>
     </row>
     <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
@@ -2441,42 +2461,50 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
     </row>
+    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A38:A40"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A29"/>
-    <mergeCell ref="A30:A36"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="A31:A37"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D9" r:id="rId1" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
-    <hyperlink ref="D13" r:id="rId2" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D17" r:id="rId3" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
-    <hyperlink ref="D20" r:id="rId4" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
-    <hyperlink ref="D22" r:id="rId5" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D30" r:id="rId6" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D32" r:id="rId7" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D31" r:id="rId8" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
-    <hyperlink ref="D18" r:id="rId9" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
-    <hyperlink ref="D35" r:id="rId10" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
-    <hyperlink ref="D34" r:id="rId11" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
-    <hyperlink ref="D33" r:id="rId12" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
-    <hyperlink ref="D28" r:id="rId13" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
-    <hyperlink ref="D29" r:id="rId14" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
-    <hyperlink ref="D36" r:id="rId15" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
-    <hyperlink ref="D25" r:id="rId16" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
-    <hyperlink ref="D26" r:id="rId17" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
-    <hyperlink ref="D24" r:id="rId18" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
-    <hyperlink ref="D27" r:id="rId19" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
-    <hyperlink ref="D21" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
+    <hyperlink ref="D10" r:id="rId1" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
+    <hyperlink ref="D14" r:id="rId2" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D18" r:id="rId3" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
+    <hyperlink ref="D21" r:id="rId4" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
+    <hyperlink ref="D23" r:id="rId5" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
+    <hyperlink ref="D31" r:id="rId6" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D33" r:id="rId7" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D32" r:id="rId8" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D19" r:id="rId9" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D36" r:id="rId10" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
+    <hyperlink ref="D35" r:id="rId11" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
+    <hyperlink ref="D34" r:id="rId12" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
+    <hyperlink ref="D29" r:id="rId13" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
+    <hyperlink ref="D30" r:id="rId14" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
+    <hyperlink ref="D37" r:id="rId15" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
+    <hyperlink ref="D26" r:id="rId16" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
+    <hyperlink ref="D27" r:id="rId17" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
+    <hyperlink ref="D25" r:id="rId18" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
+    <hyperlink ref="D28" r:id="rId19" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
+    <hyperlink ref="D22" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
     <hyperlink ref="D6" r:id="rId21" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
-    <hyperlink ref="D11" r:id="rId22" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
+    <hyperlink ref="D12" r:id="rId22" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
     <hyperlink ref="D7" r:id="rId23" xr:uid="{393AFF9D-C13B-4F2D-B7F2-228345157345}"/>
-    <hyperlink ref="D19" r:id="rId24" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
-    <hyperlink ref="D12" r:id="rId25" xr:uid="{4530051B-988E-4F1C-B60C-9AAE0AF4CF53}"/>
+    <hyperlink ref="D20" r:id="rId24" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
+    <hyperlink ref="D13" r:id="rId25" xr:uid="{4530051B-988E-4F1C-B60C-9AAE0AF4CF53}"/>
+    <hyperlink ref="D8" r:id="rId26" xr:uid="{FE5CC77A-8A35-47DD-B86E-63F037639046}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77935F9-4A00-4CC7-98C7-C128A22BEFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ECF889-A47C-4914-BBFC-7EFDAB951809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
   <si>
     <t>Main 활용</t>
   </si>
@@ -830,6 +830,18 @@
   </si>
   <si>
     <t>https://dse-sales-report-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>대용량 수요처 이상 감지 대시보드</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>YoY, 전년대비 10%이상 하락 업체 감지</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://large-volume-consumer-anomaly-alert-choihanyoub.streamlit.app/</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -915,7 +927,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -940,6 +952,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="29">
     <border>
@@ -1332,7 +1350,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1554,6 +1572,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1890,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -2070,96 +2100,96 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="72"/>
-      <c r="B14" s="55" t="s">
+    <row r="14" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="71"/>
+      <c r="B14" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="72"/>
+      <c r="B15" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C15" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="57" t="s">
+      <c r="D15" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="E15" s="56" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="44"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-    </row>
     <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+    </row>
+    <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="26" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B18" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C18" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D18" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E18" s="27" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="73" t="s">
+    <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B19" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C19" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D19" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E19" s="9" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="65"/>
-      <c r="B19" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65"/>
       <c r="B20" s="11" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>18</v>
@@ -2167,91 +2197,91 @@
     </row>
     <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="65"/>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="65"/>
+      <c r="B22" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C22" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D22" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E22" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="66"/>
-      <c r="B22" s="38" t="s">
+    <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="65"/>
+      <c r="B23" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="75" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="77" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="66"/>
+      <c r="B24" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C24" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D24" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E24" s="43" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="65" t="s">
+    <row r="25" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B25" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C25" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D25" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="42" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="65"/>
-      <c r="B24" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="65"/>
-      <c r="B25" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="42" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65"/>
-      <c r="B26" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>61</v>
+      <c r="B26" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>77</v>
       </c>
       <c r="E26" s="32" t="s">
         <v>11</v>
@@ -2260,13 +2290,13 @@
     <row r="27" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="65"/>
       <c r="B27" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" s="36" t="s">
-        <v>64</v>
+        <v>51</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="E27" s="32" t="s">
         <v>11</v>
@@ -2275,105 +2305,105 @@
     <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="65"/>
       <c r="B28" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>34</v>
+        <v>62</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="65"/>
       <c r="B29" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="65"/>
-      <c r="B30" s="11" t="s">
-        <v>55</v>
+      <c r="B30" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="65"/>
+      <c r="B31" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="65"/>
       <c r="B32" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>33</v>
+        <v>55</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="65"/>
-      <c r="B33" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>19</v>
+      <c r="A33" s="73" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="65"/>
       <c r="B34" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>35</v>
@@ -2381,85 +2411,101 @@
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="65"/>
-      <c r="B35" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>45</v>
+      <c r="B35" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="65"/>
-      <c r="B36" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>46</v>
+      <c r="B36" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>50</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="66"/>
-      <c r="B37" s="33" t="s">
+    <row r="37" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="65"/>
+      <c r="B37" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="65"/>
+      <c r="B38" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="66"/>
+      <c r="B39" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C39" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="25" t="s">
+      <c r="D39" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="35" t="s">
+      <c r="E39" s="35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="65" t="s">
+    <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="29"/>
-    </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="65"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="14"/>
-    </row>
-    <row r="40" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="66"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="24"/>
-    </row>
-    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-    </row>
-    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="29"/>
+    </row>
+    <row r="41" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="65"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="14"/>
+    </row>
+    <row r="42" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="66"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="24"/>
     </row>
     <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
@@ -2468,43 +2514,59 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
     </row>
+    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A40:A42"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="A31:A37"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="A19:A24"/>
+    <mergeCell ref="A25:A32"/>
+    <mergeCell ref="A33:A39"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D10" r:id="rId1" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
-    <hyperlink ref="D14" r:id="rId2" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D18" r:id="rId3" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
-    <hyperlink ref="D21" r:id="rId4" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
-    <hyperlink ref="D23" r:id="rId5" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D31" r:id="rId6" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D33" r:id="rId7" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D32" r:id="rId8" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
-    <hyperlink ref="D19" r:id="rId9" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
-    <hyperlink ref="D36" r:id="rId10" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
-    <hyperlink ref="D35" r:id="rId11" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
-    <hyperlink ref="D34" r:id="rId12" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
-    <hyperlink ref="D29" r:id="rId13" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
-    <hyperlink ref="D30" r:id="rId14" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
-    <hyperlink ref="D37" r:id="rId15" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
-    <hyperlink ref="D26" r:id="rId16" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
-    <hyperlink ref="D27" r:id="rId17" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
-    <hyperlink ref="D25" r:id="rId18" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
-    <hyperlink ref="D28" r:id="rId19" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
-    <hyperlink ref="D22" r:id="rId20" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
-    <hyperlink ref="D6" r:id="rId21" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
-    <hyperlink ref="D12" r:id="rId22" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
-    <hyperlink ref="D7" r:id="rId23" xr:uid="{393AFF9D-C13B-4F2D-B7F2-228345157345}"/>
-    <hyperlink ref="D20" r:id="rId24" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
-    <hyperlink ref="D13" r:id="rId25" xr:uid="{4530051B-988E-4F1C-B60C-9AAE0AF4CF53}"/>
-    <hyperlink ref="D8" r:id="rId26" xr:uid="{FE5CC77A-8A35-47DD-B86E-63F037639046}"/>
+    <hyperlink ref="D19" r:id="rId2" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
+    <hyperlink ref="D22" r:id="rId3" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
+    <hyperlink ref="D25" r:id="rId4" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
+    <hyperlink ref="D33" r:id="rId5" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D35" r:id="rId6" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D34" r:id="rId7" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D20" r:id="rId8" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D38" r:id="rId9" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
+    <hyperlink ref="D37" r:id="rId10" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
+    <hyperlink ref="D36" r:id="rId11" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
+    <hyperlink ref="D31" r:id="rId12" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
+    <hyperlink ref="D32" r:id="rId13" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
+    <hyperlink ref="D39" r:id="rId14" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
+    <hyperlink ref="D28" r:id="rId15" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
+    <hyperlink ref="D29" r:id="rId16" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
+    <hyperlink ref="D27" r:id="rId17" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
+    <hyperlink ref="D30" r:id="rId18" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
+    <hyperlink ref="D24" r:id="rId19" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
+    <hyperlink ref="D6" r:id="rId20" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
+    <hyperlink ref="D12" r:id="rId21" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
+    <hyperlink ref="D7" r:id="rId22" xr:uid="{393AFF9D-C13B-4F2D-B7F2-228345157345}"/>
+    <hyperlink ref="D21" r:id="rId23" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
+    <hyperlink ref="D13" r:id="rId24" xr:uid="{4530051B-988E-4F1C-B60C-9AAE0AF4CF53}"/>
+    <hyperlink ref="D8" r:id="rId25" xr:uid="{FE5CC77A-8A35-47DD-B86E-63F037639046}"/>
+    <hyperlink ref="D15" r:id="rId26" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D14" r:id="rId27" xr:uid="{703E5A2A-7195-429B-A1B8-23A5BC2058FB}"/>
+    <hyperlink ref="D23" r:id="rId28" xr:uid="{3AC10982-545D-4D06-B5BF-0D0400A49B77}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ECF889-A47C-4914-BBFC-7EFDAB951809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAC8CC3-A954-49B2-8C1F-F6B4AC392073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -810,9 +810,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>https://app.powerbi.com/view?r=eyJrIjoiOWIwMDZkYTEtZjM1ZS00NGE3LTg4ODktYTQ2ZjI2OWY5ZDdmIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
-  </si>
-  <si>
     <t xml:space="preserve">기온분석 및 이상기온 모니터링 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -842,6 +839,10 @@
   </si>
   <si>
     <t>https://large-volume-consumer-anomaly-alert-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/view?r=eyJrIjoiNjA5YzU5YjgtODBkYS00MjQ2LWJmOTItMmRhZWJmYzYxYzMyIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1546,6 +1547,18 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1572,18 +1585,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1930,13 +1931,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="69"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="73"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1979,7 +1980,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="74" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="45" t="s">
@@ -1996,7 +1997,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="71"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="58" t="s">
         <v>74</v>
       </c>
@@ -2011,22 +2012,22 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="71"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="D8" s="60" t="s">
         <v>86</v>
-      </c>
-      <c r="D8" s="60" t="s">
-        <v>87</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="71"/>
+      <c r="A9" s="75"/>
       <c r="B9" s="49" t="s">
         <v>8</v>
       </c>
@@ -2034,14 +2035,14 @@
         <v>9</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
+      <c r="A10" s="75"/>
       <c r="B10" s="49" t="s">
         <v>12</v>
       </c>
@@ -2056,7 +2057,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="71"/>
+      <c r="A11" s="75"/>
       <c r="B11" s="49" t="s">
         <v>36</v>
       </c>
@@ -2071,7 +2072,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="71"/>
+      <c r="A12" s="75"/>
       <c r="B12" s="52" t="s">
         <v>59</v>
       </c>
@@ -2086,12 +2087,12 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
+      <c r="A13" s="75"/>
       <c r="B13" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="64" t="s">
         <v>83</v>
-      </c>
-      <c r="C13" s="64" t="s">
-        <v>84</v>
       </c>
       <c r="D13" s="62" t="s">
         <v>81</v>
@@ -2101,22 +2102,22 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
+      <c r="A14" s="75"/>
       <c r="B14" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="64" t="s">
+      <c r="D14" s="62" t="s">
         <v>89</v>
-      </c>
-      <c r="D14" s="62" t="s">
-        <v>90</v>
       </c>
       <c r="E14" s="54" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="72"/>
+      <c r="A15" s="76"/>
       <c r="B15" s="55" t="s">
         <v>15</v>
       </c>
@@ -2164,7 +2165,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="73" t="s">
+      <c r="A19" s="77" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -2181,7 +2182,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="65"/>
+      <c r="A20" s="69"/>
       <c r="B20" s="11" t="s">
         <v>37</v>
       </c>
@@ -2196,7 +2197,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="65"/>
+      <c r="A21" s="69"/>
       <c r="B21" s="11" t="s">
         <v>79</v>
       </c>
@@ -2211,7 +2212,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="65"/>
+      <c r="A22" s="69"/>
       <c r="B22" s="15" t="s">
         <v>15</v>
       </c>
@@ -2226,22 +2227,22 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="65"/>
-      <c r="B23" s="74" t="s">
+      <c r="A23" s="69"/>
+      <c r="B23" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="75" t="s">
+      <c r="D23" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="76" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="77" t="s">
+      <c r="E23" s="68" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="66"/>
+      <c r="A24" s="70"/>
       <c r="B24" s="38" t="s">
         <v>67</v>
       </c>
@@ -2256,7 +2257,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="65" t="s">
+      <c r="A25" s="69" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="28" t="s">
@@ -2273,7 +2274,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="65"/>
+      <c r="A26" s="69"/>
       <c r="B26" s="28" t="s">
         <v>73</v>
       </c>
@@ -2288,7 +2289,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="65"/>
+      <c r="A27" s="69"/>
       <c r="B27" s="11" t="s">
         <v>51</v>
       </c>
@@ -2303,7 +2304,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="65"/>
+      <c r="A28" s="69"/>
       <c r="B28" s="17" t="s">
         <v>62</v>
       </c>
@@ -2318,7 +2319,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="65"/>
+      <c r="A29" s="69"/>
       <c r="B29" s="11" t="s">
         <v>63</v>
       </c>
@@ -2333,7 +2334,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="65"/>
+      <c r="A30" s="69"/>
       <c r="B30" s="17" t="s">
         <v>52</v>
       </c>
@@ -2348,7 +2349,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="65"/>
+      <c r="A31" s="69"/>
       <c r="B31" s="11" t="s">
         <v>54</v>
       </c>
@@ -2363,7 +2364,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="65"/>
+      <c r="A32" s="69"/>
       <c r="B32" s="11" t="s">
         <v>55</v>
       </c>
@@ -2378,7 +2379,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="73" t="s">
+      <c r="A33" s="77" t="s">
         <v>28</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -2395,7 +2396,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="65"/>
+      <c r="A34" s="69"/>
       <c r="B34" s="11" t="s">
         <v>30</v>
       </c>
@@ -2410,7 +2411,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="65"/>
+      <c r="A35" s="69"/>
       <c r="B35" s="15" t="s">
         <v>23</v>
       </c>
@@ -2425,7 +2426,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="65"/>
+      <c r="A36" s="69"/>
       <c r="B36" s="11" t="s">
         <v>49</v>
       </c>
@@ -2440,7 +2441,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="65"/>
+      <c r="A37" s="69"/>
       <c r="B37" s="17" t="s">
         <v>43</v>
       </c>
@@ -2455,7 +2456,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="65"/>
+      <c r="A38" s="69"/>
       <c r="B38" s="17" t="s">
         <v>44</v>
       </c>
@@ -2470,7 +2471,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="66"/>
+      <c r="A39" s="70"/>
       <c r="B39" s="33" t="s">
         <v>59</v>
       </c>
@@ -2485,7 +2486,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="65" t="s">
+      <c r="A40" s="69" t="s">
         <v>29</v>
       </c>
       <c r="B40" s="28"/>
@@ -2494,14 +2495,14 @@
       <c r="E40" s="29"/>
     </row>
     <row r="41" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="65"/>
+      <c r="A41" s="69"/>
       <c r="B41" s="15"/>
       <c r="C41" s="14"/>
       <c r="D41" s="13"/>
       <c r="E41" s="14"/>
     </row>
     <row r="42" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="66"/>
+      <c r="A42" s="70"/>
       <c r="B42" s="23"/>
       <c r="C42" s="24"/>
       <c r="D42" s="25"/>
@@ -2567,6 +2568,7 @@
     <hyperlink ref="D15" r:id="rId26" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
     <hyperlink ref="D14" r:id="rId27" xr:uid="{703E5A2A-7195-429B-A1B8-23A5BC2058FB}"/>
     <hyperlink ref="D23" r:id="rId28" xr:uid="{3AC10982-545D-4D06-B5BF-0D0400A49B77}"/>
+    <hyperlink ref="D9" r:id="rId29" xr:uid="{6076C444-2544-4460-8B47-7B0C1B8965F6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAC8CC3-A954-49B2-8C1F-F6B4AC392073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACB5A6D-7570-48CC-8B29-CF3C68AAA8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
+    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="93">
   <si>
     <t>Main 활용</t>
   </si>
@@ -423,10 +423,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>중장기 판매량 예측(2035년)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>과거 데이터 업로드시 중장기 공급량 예측</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -843,6 +839,18 @@
   </si>
   <si>
     <t>https://app.powerbi.com/view?r=eyJrIjoiNjA5YzU5YjgtODBkYS00MjQ2LWJmOTItMmRhZWJmYzYxYzMyIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>난방도일</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>난방도일, 냉방도일 적용</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://city-gas-supply-hdd-tracker-choihanyoub.streamlit.app/</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1984,13 +1992,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="46" t="s">
-        <v>68</v>
-      </c>
       <c r="D6" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" s="48" t="s">
         <v>7</v>
@@ -1999,13 +2007,13 @@
     <row r="7" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="75"/>
       <c r="B7" s="58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>11</v>
@@ -2014,13 +2022,13 @@
     <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="75"/>
       <c r="B8" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="D8" s="60" t="s">
         <v>85</v>
-      </c>
-      <c r="D8" s="60" t="s">
-        <v>86</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>18</v>
@@ -2035,7 +2043,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>11</v>
@@ -2074,13 +2082,13 @@
     <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="75"/>
       <c r="B12" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="53" t="s">
-        <v>60</v>
-      </c>
       <c r="D12" s="51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" s="54" t="s">
         <v>35</v>
@@ -2089,13 +2097,13 @@
     <row r="13" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="75"/>
       <c r="B13" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="64" t="s">
-        <v>83</v>
-      </c>
       <c r="D13" s="62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" s="50" t="s">
         <v>18</v>
@@ -2104,13 +2112,13 @@
     <row r="14" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="75"/>
       <c r="B14" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="64" t="s">
+      <c r="D14" s="62" t="s">
         <v>88</v>
-      </c>
-      <c r="D14" s="62" t="s">
-        <v>89</v>
       </c>
       <c r="E14" s="54" t="s">
         <v>35</v>
@@ -2199,13 +2207,13 @@
     <row r="21" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="69"/>
       <c r="B21" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>18</v>
@@ -2229,13 +2237,13 @@
     <row r="23" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="69"/>
       <c r="B23" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="66" t="s">
+      <c r="D23" s="67" t="s">
         <v>88</v>
-      </c>
-      <c r="D23" s="67" t="s">
-        <v>89</v>
       </c>
       <c r="E23" s="68" t="s">
         <v>35</v>
@@ -2244,13 +2252,13 @@
     <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="70"/>
       <c r="B24" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="39" t="s">
-        <v>68</v>
-      </c>
       <c r="D24" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24" s="43" t="s">
         <v>7</v>
@@ -2276,13 +2284,13 @@
     <row r="26" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="69"/>
       <c r="B26" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D26" s="61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E26" s="32" t="s">
         <v>11</v>
@@ -2294,10 +2302,10 @@
         <v>51</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" s="32" t="s">
         <v>11</v>
@@ -2306,13 +2314,13 @@
     <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="69"/>
       <c r="B28" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" s="32" t="s">
         <v>11</v>
@@ -2321,13 +2329,13 @@
     <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="69"/>
       <c r="B29" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="36" t="s">
         <v>63</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>64</v>
       </c>
       <c r="E29" s="32" t="s">
         <v>11</v>
@@ -2342,87 +2350,87 @@
         <v>53</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="69"/>
       <c r="B31" s="11" t="s">
         <v>54</v>
       </c>
       <c r="C31" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="16" t="s">
         <v>56</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="69"/>
-      <c r="B32" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>34</v>
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>18</v>
+      <c r="A33" s="69"/>
+      <c r="B33" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="69"/>
-      <c r="B34" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>31</v>
+      <c r="B34" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>35</v>
+        <v>24</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="69"/>
-      <c r="B35" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>32</v>
+      <c r="B35" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>91</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>19</v>
+        <v>92</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2473,13 +2481,13 @@
     <row r="39" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="70"/>
       <c r="B39" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="34" t="s">
-        <v>60</v>
-      </c>
       <c r="D39" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E39" s="35" t="s">
         <v>35</v>
@@ -2535,8 +2543,8 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A19:A24"/>
-    <mergeCell ref="A25:A32"/>
-    <mergeCell ref="A33:A39"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A32:A39"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -2544,31 +2552,31 @@
     <hyperlink ref="D19" r:id="rId2" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
     <hyperlink ref="D22" r:id="rId3" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
     <hyperlink ref="D25" r:id="rId4" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D33" r:id="rId5" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D35" r:id="rId6" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D34" r:id="rId7" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D32" r:id="rId5" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D34" r:id="rId6" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D33" r:id="rId7" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
     <hyperlink ref="D20" r:id="rId8" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
     <hyperlink ref="D38" r:id="rId9" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
     <hyperlink ref="D37" r:id="rId10" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
     <hyperlink ref="D36" r:id="rId11" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
     <hyperlink ref="D31" r:id="rId12" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
-    <hyperlink ref="D32" r:id="rId13" xr:uid="{9E0275C0-D196-4EEB-9248-B0E97EF3B232}"/>
-    <hyperlink ref="D39" r:id="rId14" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
-    <hyperlink ref="D28" r:id="rId15" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
-    <hyperlink ref="D29" r:id="rId16" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
-    <hyperlink ref="D27" r:id="rId17" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
-    <hyperlink ref="D30" r:id="rId18" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
-    <hyperlink ref="D24" r:id="rId19" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
-    <hyperlink ref="D6" r:id="rId20" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
-    <hyperlink ref="D12" r:id="rId21" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
-    <hyperlink ref="D7" r:id="rId22" xr:uid="{393AFF9D-C13B-4F2D-B7F2-228345157345}"/>
-    <hyperlink ref="D21" r:id="rId23" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
-    <hyperlink ref="D13" r:id="rId24" xr:uid="{4530051B-988E-4F1C-B60C-9AAE0AF4CF53}"/>
-    <hyperlink ref="D8" r:id="rId25" xr:uid="{FE5CC77A-8A35-47DD-B86E-63F037639046}"/>
-    <hyperlink ref="D15" r:id="rId26" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D14" r:id="rId27" xr:uid="{703E5A2A-7195-429B-A1B8-23A5BC2058FB}"/>
-    <hyperlink ref="D23" r:id="rId28" xr:uid="{3AC10982-545D-4D06-B5BF-0D0400A49B77}"/>
-    <hyperlink ref="D9" r:id="rId29" xr:uid="{6076C444-2544-4460-8B47-7B0C1B8965F6}"/>
+    <hyperlink ref="D39" r:id="rId13" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
+    <hyperlink ref="D28" r:id="rId14" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
+    <hyperlink ref="D29" r:id="rId15" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
+    <hyperlink ref="D27" r:id="rId16" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
+    <hyperlink ref="D30" r:id="rId17" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
+    <hyperlink ref="D24" r:id="rId18" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
+    <hyperlink ref="D6" r:id="rId19" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
+    <hyperlink ref="D12" r:id="rId20" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
+    <hyperlink ref="D7" r:id="rId21" xr:uid="{393AFF9D-C13B-4F2D-B7F2-228345157345}"/>
+    <hyperlink ref="D21" r:id="rId22" xr:uid="{24C65928-9510-44D1-8E63-7E41CE5ABA04}"/>
+    <hyperlink ref="D13" r:id="rId23" xr:uid="{4530051B-988E-4F1C-B60C-9AAE0AF4CF53}"/>
+    <hyperlink ref="D8" r:id="rId24" xr:uid="{FE5CC77A-8A35-47DD-B86E-63F037639046}"/>
+    <hyperlink ref="D15" r:id="rId25" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D14" r:id="rId26" xr:uid="{703E5A2A-7195-429B-A1B8-23A5BC2058FB}"/>
+    <hyperlink ref="D23" r:id="rId27" xr:uid="{3AC10982-545D-4D06-B5BF-0D0400A49B77}"/>
+    <hyperlink ref="D9" r:id="rId28" xr:uid="{6076C444-2544-4460-8B47-7B0C1B8965F6}"/>
+    <hyperlink ref="D35" r:id="rId29" xr:uid="{1DFE04E4-64C6-4391-9FA8-38D5B49B5970}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACB5A6D-7570-48CC-8B29-CF3C68AAA8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25621169-086B-4A63-99B7-15FB1966A77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="95">
   <si>
     <t>Main 활용</t>
   </si>
@@ -851,6 +851,14 @@
   </si>
   <si>
     <t>https://city-gas-supply-hdd-tracker-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>난방도일, 냉방도일 예측 모델</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HDD &amp; CDD 예측 모델</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1929,7 +1937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -2343,185 +2351,193 @@
     </row>
     <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="69"/>
-      <c r="B30" s="17" t="s">
-        <v>52</v>
+      <c r="B30" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>68</v>
+        <v>94</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>92</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="69"/>
-      <c r="B31" s="11" t="s">
-        <v>54</v>
+      <c r="B31" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="77" t="s">
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="69"/>
+      <c r="B32" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B33" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D33" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E33" s="9" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="69"/>
-      <c r="B33" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="69"/>
-      <c r="B34" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>32</v>
+      <c r="B34" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="69"/>
-      <c r="B35" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>91</v>
+      <c r="B35" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="69"/>
       <c r="B36" s="11" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="69"/>
-      <c r="B37" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>45</v>
+      <c r="B37" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>50</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="69"/>
       <c r="B38" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="69"/>
+      <c r="B39" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C39" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D39" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E39" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="70"/>
-      <c r="B39" s="33" t="s">
+    <row r="40" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="70"/>
+      <c r="B40" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C40" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="D40" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="35" t="s">
+      <c r="E40" s="35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="69" t="s">
+    <row r="41" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="29"/>
-    </row>
-    <row r="41" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="69"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="14"/>
-    </row>
-    <row r="42" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="70"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="24"/>
-    </row>
-    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="29"/>
+    </row>
+    <row r="42" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="69"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="14"/>
+    </row>
+    <row r="43" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="70"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="24"/>
     </row>
     <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
@@ -2537,14 +2553,21 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
     </row>
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="A41:A43"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A19:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A25:A32"/>
+    <mergeCell ref="A33:A40"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -2552,19 +2575,19 @@
     <hyperlink ref="D19" r:id="rId2" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
     <hyperlink ref="D22" r:id="rId3" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
     <hyperlink ref="D25" r:id="rId4" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D32" r:id="rId5" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D34" r:id="rId6" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D33" r:id="rId7" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D33" r:id="rId5" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D35" r:id="rId6" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D34" r:id="rId7" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
     <hyperlink ref="D20" r:id="rId8" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
-    <hyperlink ref="D38" r:id="rId9" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
-    <hyperlink ref="D37" r:id="rId10" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
-    <hyperlink ref="D36" r:id="rId11" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
-    <hyperlink ref="D31" r:id="rId12" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
-    <hyperlink ref="D39" r:id="rId13" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
+    <hyperlink ref="D39" r:id="rId9" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
+    <hyperlink ref="D38" r:id="rId10" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
+    <hyperlink ref="D37" r:id="rId11" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
+    <hyperlink ref="D32" r:id="rId12" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
+    <hyperlink ref="D40" r:id="rId13" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
     <hyperlink ref="D28" r:id="rId14" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
     <hyperlink ref="D29" r:id="rId15" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
     <hyperlink ref="D27" r:id="rId16" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
-    <hyperlink ref="D30" r:id="rId17" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
+    <hyperlink ref="D31" r:id="rId17" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
     <hyperlink ref="D24" r:id="rId18" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
     <hyperlink ref="D6" r:id="rId19" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
     <hyperlink ref="D12" r:id="rId20" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
@@ -2576,7 +2599,8 @@
     <hyperlink ref="D14" r:id="rId26" xr:uid="{703E5A2A-7195-429B-A1B8-23A5BC2058FB}"/>
     <hyperlink ref="D23" r:id="rId27" xr:uid="{3AC10982-545D-4D06-B5BF-0D0400A49B77}"/>
     <hyperlink ref="D9" r:id="rId28" xr:uid="{6076C444-2544-4460-8B47-7B0C1B8965F6}"/>
-    <hyperlink ref="D35" r:id="rId29" xr:uid="{1DFE04E4-64C6-4391-9FA8-38D5B49B5970}"/>
+    <hyperlink ref="D36" r:id="rId29" xr:uid="{1DFE04E4-64C6-4391-9FA8-38D5B49B5970}"/>
+    <hyperlink ref="D30" r:id="rId30" xr:uid="{49BB8314-924A-4E62-8568-989CDE58671D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub(Han hub)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25621169-086B-4A63-99B7-15FB1966A77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CF55A1-2DFA-41CD-A9A5-3FAAFD150981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="98">
   <si>
     <t>Main 활용</t>
   </si>
@@ -859,6 +859,18 @@
   </si>
   <si>
     <t>HDD &amp; CDD 예측 모델</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간대별 기온 적용 예측(for 사업계획)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://hourly-temp-supply-simulator-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HDD &amp; CDD(시간대별 기온) vs 3차 다항식(일평균기온) 비교</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1937,7 +1949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -2321,14 +2333,14 @@
     </row>
     <row r="28" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="69"/>
-      <c r="B28" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="36" t="s">
-        <v>60</v>
+      <c r="B28" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>96</v>
       </c>
       <c r="E28" s="32" t="s">
         <v>11</v>
@@ -2336,14 +2348,14 @@
     </row>
     <row r="29" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="69"/>
-      <c r="B29" s="11" t="s">
-        <v>62</v>
+      <c r="B29" s="17" t="s">
+        <v>61</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E29" s="32" t="s">
         <v>11</v>
@@ -2352,199 +2364,207 @@
     <row r="30" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="69"/>
       <c r="B30" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>94</v>
+        <v>62</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>70</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>34</v>
+        <v>63</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="69"/>
-      <c r="B31" s="17" t="s">
-        <v>52</v>
+      <c r="B31" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>68</v>
+        <v>94</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>92</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="69"/>
-      <c r="B32" s="11" t="s">
-        <v>54</v>
+      <c r="B32" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="77" t="s">
+    <row r="33" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="69"/>
+      <c r="B33" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B34" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C34" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D34" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E34" s="9" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="69"/>
-      <c r="B34" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="69"/>
-      <c r="B35" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>32</v>
+      <c r="B35" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="69"/>
-      <c r="B36" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>91</v>
+      <c r="B36" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="69"/>
       <c r="B37" s="11" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="69"/>
-      <c r="B38" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>45</v>
+      <c r="B38" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>50</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="69"/>
       <c r="B39" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="69"/>
+      <c r="B40" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C40" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D40" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E40" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="70"/>
-      <c r="B40" s="33" t="s">
+    <row r="41" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="70"/>
+      <c r="B41" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C41" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="D41" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="E40" s="35" t="s">
+      <c r="E41" s="35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="69" t="s">
+    <row r="42" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="29"/>
-    </row>
-    <row r="42" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="69"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="14"/>
-    </row>
-    <row r="43" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="70"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="24"/>
-    </row>
-    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="29"/>
+    </row>
+    <row r="43" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="69"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="14"/>
+    </row>
+    <row r="44" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="70"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="24"/>
     </row>
     <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
@@ -2560,14 +2580,21 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
     </row>
+    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A42:A44"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A19:A24"/>
-    <mergeCell ref="A25:A32"/>
-    <mergeCell ref="A33:A40"/>
+    <mergeCell ref="A25:A33"/>
+    <mergeCell ref="A34:A41"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -2575,19 +2602,19 @@
     <hyperlink ref="D19" r:id="rId2" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
     <hyperlink ref="D22" r:id="rId3" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
     <hyperlink ref="D25" r:id="rId4" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D33" r:id="rId5" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D35" r:id="rId6" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D34" r:id="rId7" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D34" r:id="rId5" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D36" r:id="rId6" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D35" r:id="rId7" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
     <hyperlink ref="D20" r:id="rId8" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
-    <hyperlink ref="D39" r:id="rId9" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
-    <hyperlink ref="D38" r:id="rId10" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
-    <hyperlink ref="D37" r:id="rId11" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
-    <hyperlink ref="D32" r:id="rId12" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
-    <hyperlink ref="D40" r:id="rId13" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
-    <hyperlink ref="D28" r:id="rId14" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
-    <hyperlink ref="D29" r:id="rId15" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
+    <hyperlink ref="D40" r:id="rId9" xr:uid="{F014F2EF-94D1-43E9-A0A9-6BB94CC3B3A9}"/>
+    <hyperlink ref="D39" r:id="rId10" xr:uid="{B1A41EA2-70D0-496D-8EEF-0FD23FDE4272}"/>
+    <hyperlink ref="D38" r:id="rId11" xr:uid="{354E4541-DCA7-4D9A-9FC1-96C92EFB100F}"/>
+    <hyperlink ref="D33" r:id="rId12" xr:uid="{0D7B770A-C9B6-40E8-ABF4-D7C96B086725}"/>
+    <hyperlink ref="D41" r:id="rId13" xr:uid="{23CCA998-6208-4D04-BDE1-08BF9F7A05F5}"/>
+    <hyperlink ref="D29" r:id="rId14" xr:uid="{75269FB8-2C87-4D24-A203-096740BCB5CB}"/>
+    <hyperlink ref="D30" r:id="rId15" xr:uid="{947B81F6-24B3-46A3-B4A0-7D0E287B8FE2}"/>
     <hyperlink ref="D27" r:id="rId16" xr:uid="{CF5B8F97-1D70-45D6-89E8-9FE76105C6C9}"/>
-    <hyperlink ref="D31" r:id="rId17" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
+    <hyperlink ref="D32" r:id="rId17" xr:uid="{9DEA0AF8-AC7F-4EBF-9FE8-77DD786975AE}"/>
     <hyperlink ref="D24" r:id="rId18" xr:uid="{BB1BFE7D-F86B-4B62-91C0-7807EB8C5661}"/>
     <hyperlink ref="D6" r:id="rId19" xr:uid="{D712563F-F28A-4B4B-A2B6-8BD2281CE988}"/>
     <hyperlink ref="D12" r:id="rId20" xr:uid="{EBA05BC1-058F-4840-9F24-48BDB1F5549F}"/>
@@ -2599,8 +2626,9 @@
     <hyperlink ref="D14" r:id="rId26" xr:uid="{703E5A2A-7195-429B-A1B8-23A5BC2058FB}"/>
     <hyperlink ref="D23" r:id="rId27" xr:uid="{3AC10982-545D-4D06-B5BF-0D0400A49B77}"/>
     <hyperlink ref="D9" r:id="rId28" xr:uid="{6076C444-2544-4460-8B47-7B0C1B8965F6}"/>
-    <hyperlink ref="D36" r:id="rId29" xr:uid="{1DFE04E4-64C6-4391-9FA8-38D5B49B5970}"/>
-    <hyperlink ref="D30" r:id="rId30" xr:uid="{49BB8314-924A-4E62-8568-989CDE58671D}"/>
+    <hyperlink ref="D37" r:id="rId29" xr:uid="{1DFE04E4-64C6-4391-9FA8-38D5B49B5970}"/>
+    <hyperlink ref="D31" r:id="rId30" xr:uid="{49BB8314-924A-4E62-8568-989CDE58671D}"/>
+    <hyperlink ref="D28" r:id="rId31" xr:uid="{AA927CCD-269F-4D06-91D7-7BAFF0F13007}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
